--- a/output/single-home-results.xlsx
+++ b/output/single-home-results.xlsx
@@ -1,20 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ecalia-my.sharepoint.com/personal/michael_ilewicz_ecalia_de/Documents/Documents/GitHub/heatpump-calculations/output/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="21" documentId="11_503900FCF613C816C7749C874FF6F92A7552CAB0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FAC38D1A-A313-4AA5-B7A2-172B06B6236C}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t>regular Heatpump energy consumption [kWh/year]</t>
   </si>
@@ -74,13 +93,22 @@
   </si>
   <si>
     <t>Renovations</t>
+  </si>
+  <si>
+    <t>regular Heat Pump COP</t>
+  </si>
+  <si>
+    <t>improved Heatpump COP</t>
+  </si>
+  <si>
+    <t>COP improvement</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -139,17 +167,25 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -187,7 +223,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -221,6 +257,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -255,9 +292,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -430,11 +468,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C20"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:C23"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="45.21875" customWidth="1"/>
+    <col min="2" max="2" width="13.88671875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1">
         <v>0</v>
       </c>
@@ -445,7 +487,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>18</v>
       </c>
@@ -453,7 +495,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -464,7 +506,7 @@
         <v>7355.18</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>1</v>
       </c>
@@ -475,7 +517,7 @@
         <v>2773.91</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -486,7 +528,7 @@
         <v>5756</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -497,7 +539,7 @@
         <v>2170.71</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -508,7 +550,7 @@
         <v>21.74</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -519,7 +561,7 @@
         <v>21.75</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>6</v>
       </c>
@@ -530,18 +572,18 @@
         <v>21.74</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>7</v>
       </c>
       <c r="B10">
-        <v>40.62</v>
+        <v>40.619999999999997</v>
       </c>
       <c r="C10">
         <v>9.94</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>8</v>
       </c>
@@ -552,7 +594,7 @@
         <v>1599.18</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>9</v>
       </c>
@@ -563,7 +605,7 @@
         <v>603.21</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>10</v>
       </c>
@@ -571,21 +613,21 @@
         <v>61.1</v>
       </c>
       <c r="C13">
-        <v>639.67</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
+        <v>639.66999999999996</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>11</v>
       </c>
       <c r="B14">
-        <v>283.22</v>
+        <v>283.22000000000003</v>
       </c>
       <c r="C14">
         <v>254.11</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>12</v>
       </c>
@@ -596,7 +638,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>13</v>
       </c>
@@ -607,7 +649,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>14</v>
       </c>
@@ -618,7 +660,7 @@
         <v>20130</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>15</v>
       </c>
@@ -629,7 +671,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>16</v>
       </c>
@@ -637,7 +679,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>17</v>
       </c>
@@ -645,7 +687,47 @@
         <v>0.13</v>
       </c>
     </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>20</v>
+      </c>
+      <c r="B21">
+        <f>B17/B3</f>
+        <v>4.6220291465663124</v>
+      </c>
+      <c r="C21">
+        <f>C17/C3</f>
+        <v>2.7368466849213751</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>21</v>
+      </c>
+      <c r="B22">
+        <f>B17/B5</f>
+        <v>5.3041428350595146</v>
+      </c>
+      <c r="C22">
+        <f>C17/C5</f>
+        <v>3.4972202918693536</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>22</v>
+      </c>
+      <c r="B23">
+        <f>B22/B21-1</f>
+        <v>0.14757883753284884</v>
+      </c>
+      <c r="C23">
+        <f>C22/C21-1</f>
+        <v>0.27782835302293263</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/output/single-home-results.xlsx
+++ b/output/single-home-results.xlsx
@@ -73,7 +73,7 @@
     <t>New homes</t>
   </si>
   <si>
-    <t>Renovations</t>
+    <t>stock_homes</t>
   </si>
 </sst>
 </file>
@@ -535,10 +535,10 @@
         <v>7</v>
       </c>
       <c r="B10">
-        <v>40.62</v>
+        <v>42.12</v>
       </c>
       <c r="C10">
-        <v>9.94</v>
+        <v>12.21</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -568,10 +568,10 @@
         <v>10</v>
       </c>
       <c r="B13">
-        <v>61.1</v>
+        <v>53.46</v>
       </c>
       <c r="C13">
-        <v>639.67</v>
+        <v>559.71</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -579,10 +579,10 @@
         <v>11</v>
       </c>
       <c r="B14">
-        <v>283.22</v>
+        <v>263.6</v>
       </c>
       <c r="C14">
-        <v>254.11</v>
+        <v>280.22</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -634,7 +634,7 @@
         <v>16</v>
       </c>
       <c r="B19">
-        <v>0.4</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -642,7 +642,7 @@
         <v>17</v>
       </c>
       <c r="B20">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
     </row>
   </sheetData>
